--- a/Liceo/gradebooks.xlsx
+++ b/Liceo/gradebooks.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\egaib\Desktop\Programación\iSams\Liceo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2908C9-B99F-4B44-9F20-C4CB00436A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858ED96D-B0D8-4A0D-BDF8-D773212CD37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{07FDE599-06F5-4538-BF53-D5B721F9DD4B}"/>
+    <workbookView xWindow="3360" yWindow="2955" windowWidth="21600" windowHeight="11295" xr2:uid="{07FDE599-06F5-4538-BF53-D5B721F9DD4B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Codes" sheetId="1" r:id="rId1"/>
+    <sheet name="codes" sheetId="1" r:id="rId1"/>
     <sheet name="Grades" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -23,6 +23,1712 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="567">
+  <si>
+    <t>10EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>10EGB-A ART</t>
+  </si>
+  <si>
+    <t>10EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>10EGB-A CIVICS</t>
+  </si>
+  <si>
+    <t>10EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>10EGB-A DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>10EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>10EGB-A EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>10EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>10EGB-A INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>10EGB-A LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>10EGB-A LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>10EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>10EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>10EGB-A MUSIC</t>
+  </si>
+  <si>
+    <t>10EGB-A ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>10EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>10EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>10EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>10EGB-B ART</t>
+  </si>
+  <si>
+    <t>10EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>10EGB-B CIVICS</t>
+  </si>
+  <si>
+    <t>10EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>10EGB-B DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>10EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>10EGB-B EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>10EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>10EGB-B INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>10EGB-B LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>10EGB-B LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>10EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>10EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>10EGB-B MUSIC</t>
+  </si>
+  <si>
+    <t>10EGB-B ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>10EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>10EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>10EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>10EGB-C ART</t>
+  </si>
+  <si>
+    <t>10EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>10EGB-C CIVICS</t>
+  </si>
+  <si>
+    <t>10EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>10EGB-C DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>10EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>10EGB-C EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>10EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>10EGB-C INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>10EGB-C LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>10EGB-C LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>10EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>10EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>10EGB-C MUSIC</t>
+  </si>
+  <si>
+    <t>10EGB-C ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>10EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>10EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>1BCH-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>1BCH-A BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>1BCH-A CIVICS</t>
+  </si>
+  <si>
+    <t>1BCH-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>1BCH-A DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>1BCH-A EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>1BCH-A FILOSOFÍA/THEORY OF KNOWLEDGE</t>
+  </si>
+  <si>
+    <t>1BCH-A FÍSICA</t>
+  </si>
+  <si>
+    <t>1BCH-A INDIVIDUALS AND SOCIETIES (HISTORY)</t>
+  </si>
+  <si>
+    <t>1BCH-A LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>1BCH-A LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>1BCH-A LENGUA Y LITERATURA</t>
+  </si>
+  <si>
+    <t>1BCH-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>1BCH-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>1BCH-A QUÍMICA</t>
+  </si>
+  <si>
+    <t>1BCH-A VISUAL ARTS</t>
+  </si>
+  <si>
+    <t>1BCH-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>1BCH-B BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>1BCH-B CIVICS</t>
+  </si>
+  <si>
+    <t>1BCH-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>1BCH-B DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>1BCH-B EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>1BCH-B FILOSOFÍA/THEORY OF KNOWLEDGE</t>
+  </si>
+  <si>
+    <t>1BCH-B FÍSICA</t>
+  </si>
+  <si>
+    <t>1BCH-B INDIVIDUALS AND SOCIETIES (HISTORY)</t>
+  </si>
+  <si>
+    <t>1BCH-B LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>1BCH-B LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>1BCH-B LENGUA Y LITERATURA</t>
+  </si>
+  <si>
+    <t>1BCH-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>1BCH-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>1BCH-B QUÍMICA</t>
+  </si>
+  <si>
+    <t>1BCH-B VISUAL ARTS</t>
+  </si>
+  <si>
+    <t>1BCH-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>1BCH-C BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>1BCH-C CIVICS</t>
+  </si>
+  <si>
+    <t>1BCH-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>1BCH-C DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>1BCH-C EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>1BCH-C FILOSOFÍA/THEORY OF KNOWLEDGE</t>
+  </si>
+  <si>
+    <t>1BCH-C FÍSICA</t>
+  </si>
+  <si>
+    <t>1BCH-C INDIVIDUALS AND SOCIETIES (HISTORY)</t>
+  </si>
+  <si>
+    <t>1BCH-C LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>1BCH-C LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>1BCH-C LENGUA Y LITERATURA</t>
+  </si>
+  <si>
+    <t>1BCH-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>1BCH-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>1BCH-C QUÍMICA</t>
+  </si>
+  <si>
+    <t>1BCH-C VISUAL ARTS</t>
+  </si>
+  <si>
+    <t>1EGB-A master inicial</t>
+  </si>
+  <si>
+    <t>2BCH-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>2BCH-A Biología NM IB</t>
+  </si>
+  <si>
+    <t>2BCH-A CAS</t>
+  </si>
+  <si>
+    <t>2BCH-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>2BCH-A EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>2BCH-A English B NS IB</t>
+  </si>
+  <si>
+    <t>2BCH-A FÍSICA</t>
+  </si>
+  <si>
+    <t>2BCH-A History NS IB</t>
+  </si>
+  <si>
+    <t>2BCH-A Lengua A: Lengua y Literatura NS IB</t>
+  </si>
+  <si>
+    <t>2BCH-A Matemática: Aplicaciones e Interpretaciones NM IB</t>
+  </si>
+  <si>
+    <t>2BCH-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>2BCH-A QUÍMICA</t>
+  </si>
+  <si>
+    <t>2BCH-A TOK: Theory of Knowledge</t>
+  </si>
+  <si>
+    <t>2BCH-A Visual Arts NM IB</t>
+  </si>
+  <si>
+    <t>2BCH-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>2BCH-B Biología NM IB</t>
+  </si>
+  <si>
+    <t>2BCH-B CAS</t>
+  </si>
+  <si>
+    <t>2BCH-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>2BCH-B EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>2BCH-B English B NS IB</t>
+  </si>
+  <si>
+    <t>2BCH-B FÍSICA</t>
+  </si>
+  <si>
+    <t>2BCH-B History NS IB</t>
+  </si>
+  <si>
+    <t>2BCH-B Lengua A: Lengua y Literatura NS IB</t>
+  </si>
+  <si>
+    <t>2BCH-B Matemática: Aplicaciones e Interpretaciones NM IB</t>
+  </si>
+  <si>
+    <t>2BCH-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>2BCH-B QUÍMICA</t>
+  </si>
+  <si>
+    <t>2BCH-B TOK: Theory of Knowledge</t>
+  </si>
+  <si>
+    <t>2BCH-B Visual Arts NM IB</t>
+  </si>
+  <si>
+    <t>2EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>2EGB-A Art</t>
+  </si>
+  <si>
+    <t>2EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>2EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>2EGB-A DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>2EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>2EGB-A EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>2EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>2EGB-A EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>2EGB-A ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>2EGB-A LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>2EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>2EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>2EGB-A Música</t>
+  </si>
+  <si>
+    <t>2EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>2EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>2EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>2EGB-B Art</t>
+  </si>
+  <si>
+    <t>2EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>2EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>2EGB-B DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>2EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>2EGB-B EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>2EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>2EGB-B EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>2EGB-B ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>2EGB-B LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>2EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>2EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>2EGB-B Música</t>
+  </si>
+  <si>
+    <t>2EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>2EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>2EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>2EGB-C Art</t>
+  </si>
+  <si>
+    <t>2EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>2EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>2EGB-C DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>2EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>2EGB-C EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>2EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>2EGB-C EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>2EGB-C ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>2EGB-C LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>2EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>2EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>2EGB-C Música</t>
+  </si>
+  <si>
+    <t>2EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>2EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>3BCH-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>3BCH-A CAS</t>
+  </si>
+  <si>
+    <t>3BCH-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>3BCH-A EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>3BCH-A English B NS IB</t>
+  </si>
+  <si>
+    <t>3BCH-A FÍSICA</t>
+  </si>
+  <si>
+    <t>3BCH-A History NS IB</t>
+  </si>
+  <si>
+    <t>3BCH-A Lengua A: Lengua y Literatura NS IB</t>
+  </si>
+  <si>
+    <t>3BCH-A Matemática: Aplicaciones e Interpretaciones NM IB</t>
+  </si>
+  <si>
+    <t>3BCH-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>3BCH-A QUÍMICA</t>
+  </si>
+  <si>
+    <t>3BCH-A TOK: Theory of Knowledge</t>
+  </si>
+  <si>
+    <t>3BCH-A Visual Arts NM IB</t>
+  </si>
+  <si>
+    <t>3BCH-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>3BCH-B Biología NM IB</t>
+  </si>
+  <si>
+    <t>3BCH-B CAS</t>
+  </si>
+  <si>
+    <t>3BCH-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>3BCH-B EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>3BCH-B English B NS IB</t>
+  </si>
+  <si>
+    <t>3BCH-B FÍSICA</t>
+  </si>
+  <si>
+    <t>3BCH-B History NS IB</t>
+  </si>
+  <si>
+    <t>3BCH-B Lengua A: Lengua y Literatura NS IB</t>
+  </si>
+  <si>
+    <t>3BCH-B Matemática: Aplicaciones e Interpretaciones NM IB</t>
+  </si>
+  <si>
+    <t>3BCH-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>3BCH-B QUÍMICA</t>
+  </si>
+  <si>
+    <t>3BCH-B TOK: Theory of Knowledge</t>
+  </si>
+  <si>
+    <t>3BCH-B Visual Arts NM IB</t>
+  </si>
+  <si>
+    <t>3EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>3EGB-A Art</t>
+  </si>
+  <si>
+    <t>3EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>3EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>3EGB-A DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>3EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>3EGB-A EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>3EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>3EGB-A EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>3EGB-A ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>3EGB-A LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>3EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>3EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>3EGB-A Música</t>
+  </si>
+  <si>
+    <t>3EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>3EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>3EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>3EGB-B Art</t>
+  </si>
+  <si>
+    <t>3EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>3EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>3EGB-B DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>3EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>3EGB-B EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>3EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>3EGB-B EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>3EGB-B ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>3EGB-B LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>3EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>3EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>3EGB-B Música</t>
+  </si>
+  <si>
+    <t>3EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>3EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>3EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>3EGB-C Art</t>
+  </si>
+  <si>
+    <t>3EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>3EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>3EGB-C DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>3EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>3EGB-C EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>3EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>3EGB-C EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>3EGB-C ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>3EGB-C LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>3EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>3EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>3EGB-C Música</t>
+  </si>
+  <si>
+    <t>3EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>3EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>4EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>4EGB-A Art</t>
+  </si>
+  <si>
+    <t>4EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>4EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>4EGB-A DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>4EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>4EGB-A EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>4EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>4EGB-A EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>4EGB-A ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>4EGB-A LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>4EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>4EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>4EGB-A Música</t>
+  </si>
+  <si>
+    <t>4EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>4EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>4EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>4EGB-B Art</t>
+  </si>
+  <si>
+    <t>4EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>4EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>4EGB-B DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>4EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>4EGB-B EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>4EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>4EGB-B EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>4EGB-B ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>4EGB-B LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>4EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>4EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>4EGB-B Música</t>
+  </si>
+  <si>
+    <t>4EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>4EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>4EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>4EGB-C Art</t>
+  </si>
+  <si>
+    <t>4EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>4EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>4EGB-C DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>4EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>4EGB-C EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>4EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>4EGB-C EDUCACIÓN PERSONAL, SOCIAL Y FÍSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>4EGB-C ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>4EGB-C LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>4EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>4EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>4EGB-C Música</t>
+  </si>
+  <si>
+    <t>4EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>4EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>5EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>5EGB-A Art</t>
+  </si>
+  <si>
+    <t>5EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>5EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>5EGB-A DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>5EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>5EGB-A EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>5EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>5EGB-A EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>5EGB-A ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>5EGB-A LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>5EGB-A LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>5EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>5EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>5EGB-A Música</t>
+  </si>
+  <si>
+    <t>5EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>5EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>5EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>5EGB-B Art</t>
+  </si>
+  <si>
+    <t>5EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>5EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>5EGB-B DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>5EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>5EGB-B EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>5EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>5EGB-B EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>5EGB-B ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>5EGB-B LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>5EGB-B LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>5EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>5EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>5EGB-B Música</t>
+  </si>
+  <si>
+    <t>5EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>5EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>5EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>5EGB-C Art</t>
+  </si>
+  <si>
+    <t>5EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>5EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>5EGB-C DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>5EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>5EGB-C EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>5EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>5EGB-C EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>5EGB-C ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>5EGB-C LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>5EGB-C LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>5EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>5EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>5EGB-C Música</t>
+  </si>
+  <si>
+    <t>5EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>5EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>6EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>6EGB-A Art</t>
+  </si>
+  <si>
+    <t>6EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>6EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>6EGB-A DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>6EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>6EGB-A EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>6EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>6EGB-A EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>6EGB-A ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>6EGB-A LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>6EGB-A LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>6EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>6EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>6EGB-A Música</t>
+  </si>
+  <si>
+    <t>6EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>6EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>6EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>6EGB-B Art</t>
+  </si>
+  <si>
+    <t>6EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>6EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>6EGB-B DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>6EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>6EGB-B EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>6EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>6EGB-B EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>6EGB-B ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>6EGB-B LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>6EGB-B LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>6EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>6EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>6EGB-B Música</t>
+  </si>
+  <si>
+    <t>6EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>6EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>6EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>6EGB-C Art</t>
+  </si>
+  <si>
+    <t>6EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>6EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>6EGB-C DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>6EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>6EGB-C EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>6EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>6EGB-C EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>6EGB-C ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>6EGB-C LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>6EGB-C LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>6EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>6EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>6EGB-C Música</t>
+  </si>
+  <si>
+    <t>6EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>6EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>7EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE (4)</t>
+  </si>
+  <si>
+    <t>7EGB-A Art</t>
+  </si>
+  <si>
+    <t>7EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>7EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>7EGB-A DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>7EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>7EGB-A EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>7EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>7EGB-A EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>7EGB-A ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>7EGB-A LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>7EGB-A LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>7EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>7EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>7EGB-A Música</t>
+  </si>
+  <si>
+    <t>7EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>7EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>7EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>7EGB-B Art</t>
+  </si>
+  <si>
+    <t>7EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>7EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>7EGB-B DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>7EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>7EGB-B EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>7EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>7EGB-B EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>7EGB-B ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>7EGB-B LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>7EGB-B LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>7EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>7EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>7EGB-B Música</t>
+  </si>
+  <si>
+    <t>7EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>7EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>7EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA/HABLEMOS DE APRENDIZAJE</t>
+  </si>
+  <si>
+    <t>7EGB-C Art</t>
+  </si>
+  <si>
+    <t>7EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>7EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>7EGB-C DIGITAL LEARNING</t>
+  </si>
+  <si>
+    <t>7EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>7EGB-C EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>7EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>7EGB-C EDUCACIÒN PERSONAL, SOCIAL Y FÌSICA/CÍVICA</t>
+  </si>
+  <si>
+    <t>7EGB-C ESTUDIOS SOCIALES</t>
+  </si>
+  <si>
+    <t>7EGB-C LANGUAGE ACQUISITION (English)</t>
+  </si>
+  <si>
+    <t>7EGB-C LANGUAGE ACQUISITION (Francés)</t>
+  </si>
+  <si>
+    <t>7EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>7EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>7EGB-C Música</t>
+  </si>
+  <si>
+    <t>7EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>7EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>8EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>8EGB-A ART</t>
+  </si>
+  <si>
+    <t>8EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>8EGB-A CIVICS</t>
+  </si>
+  <si>
+    <t>8EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>8EGB-A DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>8EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>8EGB-A EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>8EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>8EGB-A INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>8EGB-A LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>8EGB-A LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>8EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>8EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>8EGB-A MUSIC</t>
+  </si>
+  <si>
+    <t>8EGB-A ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>8EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>8EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>8EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>8EGB-B ART</t>
+  </si>
+  <si>
+    <t>8EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>8EGB-B CIVICS</t>
+  </si>
+  <si>
+    <t>8EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>8EGB-B DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>8EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>8EGB-B EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>8EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>8EGB-B INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>8EGB-B LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>8EGB-B LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>8EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>8EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>8EGB-B MUSIC</t>
+  </si>
+  <si>
+    <t>8EGB-B ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>8EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>8EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>8EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>8EGB-C ART</t>
+  </si>
+  <si>
+    <t>8EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>8EGB-C CIVICS</t>
+  </si>
+  <si>
+    <t>8EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>8EGB-C DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>8EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>8EGB-C EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>8EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>8EGB-C INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>8EGB-C LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>8EGB-C LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>8EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>8EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>8EGB-C MUSIC</t>
+  </si>
+  <si>
+    <t>8EGB-C ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>8EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>8EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>9EGB-A ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>9EGB-A ART</t>
+  </si>
+  <si>
+    <t>9EGB-A CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>9EGB-A CIVICS</t>
+  </si>
+  <si>
+    <t>9EGB-A COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>9EGB-A DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>9EGB-A EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>9EGB-A EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>9EGB-A EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>9EGB-A INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>9EGB-A LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>9EGB-A LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>9EGB-A LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>9EGB-A MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>9EGB-A MUSIC</t>
+  </si>
+  <si>
+    <t>9EGB-A ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>9EGB-A PROMEDIO</t>
+  </si>
+  <si>
+    <t>9EGB-A ROBOTICS</t>
+  </si>
+  <si>
+    <t>9EGB-B ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>9EGB-B ART</t>
+  </si>
+  <si>
+    <t>9EGB-B CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>9EGB-B CIVICS</t>
+  </si>
+  <si>
+    <t>9EGB-B COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>9EGB-B DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>9EGB-B EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>9EGB-B EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>9EGB-B EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>9EGB-B INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>9EGB-B LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>9EGB-B LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>9EGB-B LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>9EGB-B MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>9EGB-B MUSIC</t>
+  </si>
+  <si>
+    <t>9EGB-B ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>9EGB-B PROMEDIO</t>
+  </si>
+  <si>
+    <t>9EGB-B ROBOTICS</t>
+  </si>
+  <si>
+    <t>9EGB-C ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>9EGB-C ART</t>
+  </si>
+  <si>
+    <t>9EGB-C CIENCIAS NATURALES</t>
+  </si>
+  <si>
+    <t>9EGB-C CIVICS</t>
+  </si>
+  <si>
+    <t>9EGB-C COMPORTAMIENTO</t>
+  </si>
+  <si>
+    <t>9EGB-C DISEÑO/ LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>9EGB-C EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>9EGB-C EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+  </si>
+  <si>
+    <t>9EGB-C EDUCACIÓN PARA LA VIDA/FORMACIÓN CRISTIANA</t>
+  </si>
+  <si>
+    <t>9EGB-C INDIVIDUALS AND SOCIETIES (History)</t>
+  </si>
+  <si>
+    <t>9EGB-C LANGUAGE ACQUISITION (French)</t>
+  </si>
+  <si>
+    <t>9EGB-C LANGUAGE AND LITERATURE</t>
+  </si>
+  <si>
+    <t>9EGB-C LENGUA Y LITERATURA/ ANIMACIÓN A LA LECTURA</t>
+  </si>
+  <si>
+    <t>9EGB-C MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>9EGB-C MUSIC</t>
+  </si>
+  <si>
+    <t>9EGB-C ORIENTACIÓN VOCACIONAL Y PROFESIONAL</t>
+  </si>
+  <si>
+    <t>9EGB-C PROMEDIO</t>
+  </si>
+  <si>
+    <t>9EGB-C ROBOTICS</t>
+  </si>
+  <si>
+    <t>EGB EDUCACIÓN CULTURAL Y ARTÍSTICA</t>
+  </si>
+  <si>
+    <t>TEST GRADEBOOK 2026-2027</t>
+  </si>
+  <si>
+    <t>Materia</t>
+  </si>
+  <si>
+    <t>Codigo</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -372,9 +2078,4546 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C953D95B-C2AC-4B72-BC5F-30A0FB5C310F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2417</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2585</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2510</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2549</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2594</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2697</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2567</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2426</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2540</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2558</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2519</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2468</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2477</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2576</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2387</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2709</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2450</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2418</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2586</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2511</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2550</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2595</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2698</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2568</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2427</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2541</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2559</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2520</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2469</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2478</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2577</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2388</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2710</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2451</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2419</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2587</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2512</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2551</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2136</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2596</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2699</v>
+      </c>
+      <c r="B44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2569</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2428</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2542</v>
+      </c>
+      <c r="B47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2560</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2521</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2470</v>
+      </c>
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>781</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2479</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2578</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2389</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2711</v>
+      </c>
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2452</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2157</v>
+      </c>
+      <c r="B57" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2195</v>
+      </c>
+      <c r="B58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2180</v>
+      </c>
+      <c r="B59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2137</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2210</v>
+      </c>
+      <c r="B61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2207</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2183</v>
+      </c>
+      <c r="B63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2201</v>
+      </c>
+      <c r="B64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2177</v>
+      </c>
+      <c r="B65" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2174</v>
+      </c>
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2219</v>
+      </c>
+      <c r="B67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2216</v>
+      </c>
+      <c r="B68" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2171</v>
+      </c>
+      <c r="B69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2713</v>
+      </c>
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2204</v>
+      </c>
+      <c r="B72" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2158</v>
+      </c>
+      <c r="B73" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2196</v>
+      </c>
+      <c r="B74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2181</v>
+      </c>
+      <c r="B75" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2138</v>
+      </c>
+      <c r="B76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2211</v>
+      </c>
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2208</v>
+      </c>
+      <c r="B78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2184</v>
+      </c>
+      <c r="B79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2202</v>
+      </c>
+      <c r="B80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2178</v>
+      </c>
+      <c r="B81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2175</v>
+      </c>
+      <c r="B82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2220</v>
+      </c>
+      <c r="B83" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2217</v>
+      </c>
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2172</v>
+      </c>
+      <c r="B85" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2714</v>
+      </c>
+      <c r="B86" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2199</v>
+      </c>
+      <c r="B87" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2205</v>
+      </c>
+      <c r="B88" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2159</v>
+      </c>
+      <c r="B89" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2197</v>
+      </c>
+      <c r="B90" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2182</v>
+      </c>
+      <c r="B91" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2139</v>
+      </c>
+      <c r="B92" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2212</v>
+      </c>
+      <c r="B93" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2209</v>
+      </c>
+      <c r="B94" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2185</v>
+      </c>
+      <c r="B95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2203</v>
+      </c>
+      <c r="B96" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2179</v>
+      </c>
+      <c r="B97" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2176</v>
+      </c>
+      <c r="B98" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>2221</v>
+      </c>
+      <c r="B99" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2218</v>
+      </c>
+      <c r="B100" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2173</v>
+      </c>
+      <c r="B101" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2715</v>
+      </c>
+      <c r="B102" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2200</v>
+      </c>
+      <c r="B103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2206</v>
+      </c>
+      <c r="B104" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2742</v>
+      </c>
+      <c r="B105" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2240</v>
+      </c>
+      <c r="B106" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2295</v>
+      </c>
+      <c r="B107" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2244</v>
+      </c>
+      <c r="B108" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2140</v>
+      </c>
+      <c r="B109" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2354</v>
+      </c>
+      <c r="B110" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>2283</v>
+      </c>
+      <c r="B111" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2342</v>
+      </c>
+      <c r="B112" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>2287</v>
+      </c>
+      <c r="B113" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>2257</v>
+      </c>
+      <c r="B114" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>2261</v>
+      </c>
+      <c r="B115" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>2738</v>
+      </c>
+      <c r="B116" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>2338</v>
+      </c>
+      <c r="B117" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>2291</v>
+      </c>
+      <c r="B118" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>2346</v>
+      </c>
+      <c r="B119" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>2241</v>
+      </c>
+      <c r="B120" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>2296</v>
+      </c>
+      <c r="B121" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>2245</v>
+      </c>
+      <c r="B122" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>2141</v>
+      </c>
+      <c r="B123" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>2355</v>
+      </c>
+      <c r="B124" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>2284</v>
+      </c>
+      <c r="B125" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2343</v>
+      </c>
+      <c r="B126" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2288</v>
+      </c>
+      <c r="B127" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>2258</v>
+      </c>
+      <c r="B128" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2262</v>
+      </c>
+      <c r="B129" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>2739</v>
+      </c>
+      <c r="B130" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2339</v>
+      </c>
+      <c r="B131" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2292</v>
+      </c>
+      <c r="B132" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2347</v>
+      </c>
+      <c r="B133" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2317</v>
+      </c>
+      <c r="B134" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2231</v>
+      </c>
+      <c r="B135" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>2429</v>
+      </c>
+      <c r="B136" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>2111</v>
+      </c>
+      <c r="B137" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>2299</v>
+      </c>
+      <c r="B138" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>2729</v>
+      </c>
+      <c r="B139" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>2248</v>
+      </c>
+      <c r="B140" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>2265</v>
+      </c>
+      <c r="B141" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2480</v>
+      </c>
+      <c r="B142" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>2453</v>
+      </c>
+      <c r="B143" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>2495</v>
+      </c>
+      <c r="B144" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>2360</v>
+      </c>
+      <c r="B145" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>2402</v>
+      </c>
+      <c r="B146" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>2222</v>
+      </c>
+      <c r="B147" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>2716</v>
+      </c>
+      <c r="B148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>2308</v>
+      </c>
+      <c r="B149" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>2318</v>
+      </c>
+      <c r="B150" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>2232</v>
+      </c>
+      <c r="B151" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>2430</v>
+      </c>
+      <c r="B152" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>2112</v>
+      </c>
+      <c r="B153" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>2300</v>
+      </c>
+      <c r="B154" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>2730</v>
+      </c>
+      <c r="B155" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>2249</v>
+      </c>
+      <c r="B156" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>2266</v>
+      </c>
+      <c r="B157" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>2481</v>
+      </c>
+      <c r="B158" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>2454</v>
+      </c>
+      <c r="B159" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>2496</v>
+      </c>
+      <c r="B160" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>2361</v>
+      </c>
+      <c r="B161" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>2403</v>
+      </c>
+      <c r="B162" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>2223</v>
+      </c>
+      <c r="B163" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>2717</v>
+      </c>
+      <c r="B164" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>2309</v>
+      </c>
+      <c r="B165" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>2319</v>
+      </c>
+      <c r="B166" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>2233</v>
+      </c>
+      <c r="B167" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>2431</v>
+      </c>
+      <c r="B168" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>2113</v>
+      </c>
+      <c r="B169" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>2301</v>
+      </c>
+      <c r="B170" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>2731</v>
+      </c>
+      <c r="B171" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>2250</v>
+      </c>
+      <c r="B172" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>2267</v>
+      </c>
+      <c r="B173" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>2482</v>
+      </c>
+      <c r="B174" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>2455</v>
+      </c>
+      <c r="B175" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>2497</v>
+      </c>
+      <c r="B176" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>2362</v>
+      </c>
+      <c r="B177" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>2404</v>
+      </c>
+      <c r="B178" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>2224</v>
+      </c>
+      <c r="B179" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>2718</v>
+      </c>
+      <c r="B180" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>2310</v>
+      </c>
+      <c r="B181" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>2242</v>
+      </c>
+      <c r="B182" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>2246</v>
+      </c>
+      <c r="B183" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>2142</v>
+      </c>
+      <c r="B184" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>2356</v>
+      </c>
+      <c r="B185" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>2285</v>
+      </c>
+      <c r="B186" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>2344</v>
+      </c>
+      <c r="B187" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>2289</v>
+      </c>
+      <c r="B188" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>2259</v>
+      </c>
+      <c r="B189" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>2263</v>
+      </c>
+      <c r="B190" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>2740</v>
+      </c>
+      <c r="B191" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>2340</v>
+      </c>
+      <c r="B192" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>2293</v>
+      </c>
+      <c r="B193" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>2348</v>
+      </c>
+      <c r="B194" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>2243</v>
+      </c>
+      <c r="B195" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>2298</v>
+      </c>
+      <c r="B196" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>2247</v>
+      </c>
+      <c r="B197" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>2143</v>
+      </c>
+      <c r="B198" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>2357</v>
+      </c>
+      <c r="B199" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>2286</v>
+      </c>
+      <c r="B200" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>2345</v>
+      </c>
+      <c r="B201" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>2290</v>
+      </c>
+      <c r="B202" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>2260</v>
+      </c>
+      <c r="B203" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>2264</v>
+      </c>
+      <c r="B204" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>2741</v>
+      </c>
+      <c r="B205" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>2341</v>
+      </c>
+      <c r="B206" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>2294</v>
+      </c>
+      <c r="B207" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>2349</v>
+      </c>
+      <c r="B208" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>2320</v>
+      </c>
+      <c r="B209" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>2234</v>
+      </c>
+      <c r="B210" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>2432</v>
+      </c>
+      <c r="B211" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>2124</v>
+      </c>
+      <c r="B212" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>2302</v>
+      </c>
+      <c r="B213" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>2732</v>
+      </c>
+      <c r="B214" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>2251</v>
+      </c>
+      <c r="B215" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>2268</v>
+      </c>
+      <c r="B216" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>2483</v>
+      </c>
+      <c r="B217" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>2456</v>
+      </c>
+      <c r="B218" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>2498</v>
+      </c>
+      <c r="B219" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>2363</v>
+      </c>
+      <c r="B220" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>2405</v>
+      </c>
+      <c r="B221" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>2225</v>
+      </c>
+      <c r="B222" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>2720</v>
+      </c>
+      <c r="B223" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>2311</v>
+      </c>
+      <c r="B224" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>2321</v>
+      </c>
+      <c r="B225" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>2235</v>
+      </c>
+      <c r="B226" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>2433</v>
+      </c>
+      <c r="B227" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>2114</v>
+      </c>
+      <c r="B228" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>2303</v>
+      </c>
+      <c r="B229" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>2733</v>
+      </c>
+      <c r="B230" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>2252</v>
+      </c>
+      <c r="B231" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>2269</v>
+      </c>
+      <c r="B232" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>2484</v>
+      </c>
+      <c r="B233" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>2457</v>
+      </c>
+      <c r="B234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>2499</v>
+      </c>
+      <c r="B235" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>2364</v>
+      </c>
+      <c r="B236" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>2406</v>
+      </c>
+      <c r="B237" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>2226</v>
+      </c>
+      <c r="B238" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>2721</v>
+      </c>
+      <c r="B239" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>2312</v>
+      </c>
+      <c r="B240" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>2322</v>
+      </c>
+      <c r="B241" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>2236</v>
+      </c>
+      <c r="B242" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>2434</v>
+      </c>
+      <c r="B243" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>2115</v>
+      </c>
+      <c r="B244" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>2304</v>
+      </c>
+      <c r="B245" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>2734</v>
+      </c>
+      <c r="B246" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>2253</v>
+      </c>
+      <c r="B247" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>2270</v>
+      </c>
+      <c r="B248" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>2485</v>
+      </c>
+      <c r="B249" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>2458</v>
+      </c>
+      <c r="B250" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>2500</v>
+      </c>
+      <c r="B251" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2365</v>
+      </c>
+      <c r="B252" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>2407</v>
+      </c>
+      <c r="B253" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>2227</v>
+      </c>
+      <c r="B254" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>2722</v>
+      </c>
+      <c r="B255" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>2313</v>
+      </c>
+      <c r="B256" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>2323</v>
+      </c>
+      <c r="B257" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>2237</v>
+      </c>
+      <c r="B258" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>2435</v>
+      </c>
+      <c r="B259" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>2116</v>
+      </c>
+      <c r="B260" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>2305</v>
+      </c>
+      <c r="B261" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>2735</v>
+      </c>
+      <c r="B262" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>2254</v>
+      </c>
+      <c r="B263" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>2271</v>
+      </c>
+      <c r="B264" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>2486</v>
+      </c>
+      <c r="B265" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>2459</v>
+      </c>
+      <c r="B266" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>2501</v>
+      </c>
+      <c r="B267" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>2366</v>
+      </c>
+      <c r="B268" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>2408</v>
+      </c>
+      <c r="B269" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>2228</v>
+      </c>
+      <c r="B270" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>2723</v>
+      </c>
+      <c r="B271" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>2314</v>
+      </c>
+      <c r="B272" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>2324</v>
+      </c>
+      <c r="B273" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>2238</v>
+      </c>
+      <c r="B274" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>2436</v>
+      </c>
+      <c r="B275" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>2117</v>
+      </c>
+      <c r="B276" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>2306</v>
+      </c>
+      <c r="B277" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>2736</v>
+      </c>
+      <c r="B278" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>2255</v>
+      </c>
+      <c r="B279" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>2272</v>
+      </c>
+      <c r="B280" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>2487</v>
+      </c>
+      <c r="B281" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>2460</v>
+      </c>
+      <c r="B282" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>2502</v>
+      </c>
+      <c r="B283" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>2367</v>
+      </c>
+      <c r="B284" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>2409</v>
+      </c>
+      <c r="B285" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>2229</v>
+      </c>
+      <c r="B286" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>2724</v>
+      </c>
+      <c r="B287" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>2315</v>
+      </c>
+      <c r="B288" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>2325</v>
+      </c>
+      <c r="B289" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>2239</v>
+      </c>
+      <c r="B290" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>2437</v>
+      </c>
+      <c r="B291" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>2118</v>
+      </c>
+      <c r="B292" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>2307</v>
+      </c>
+      <c r="B293" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>2737</v>
+      </c>
+      <c r="B294" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>2256</v>
+      </c>
+      <c r="B295" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>2273</v>
+      </c>
+      <c r="B296" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>2488</v>
+      </c>
+      <c r="B297" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>2461</v>
+      </c>
+      <c r="B298" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>2503</v>
+      </c>
+      <c r="B299" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>2368</v>
+      </c>
+      <c r="B300" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>2410</v>
+      </c>
+      <c r="B301" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>2230</v>
+      </c>
+      <c r="B302" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>2725</v>
+      </c>
+      <c r="B303" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>2316</v>
+      </c>
+      <c r="B304" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>2326</v>
+      </c>
+      <c r="B305" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>2603</v>
+      </c>
+      <c r="B306" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>2390</v>
+      </c>
+      <c r="B307" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>2119</v>
+      </c>
+      <c r="B308" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>2213</v>
+      </c>
+      <c r="B309" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>2616</v>
+      </c>
+      <c r="B310" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>2609</v>
+      </c>
+      <c r="B311" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>2274</v>
+      </c>
+      <c r="B312" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>2489</v>
+      </c>
+      <c r="B313" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>2396</v>
+      </c>
+      <c r="B314" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>2522</v>
+      </c>
+      <c r="B315" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>2528</v>
+      </c>
+      <c r="B316" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>2369</v>
+      </c>
+      <c r="B317" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>2375</v>
+      </c>
+      <c r="B318" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>2597</v>
+      </c>
+      <c r="B319" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>2654</v>
+      </c>
+      <c r="B320" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>2277</v>
+      </c>
+      <c r="B321" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>2327</v>
+      </c>
+      <c r="B322" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>2604</v>
+      </c>
+      <c r="B323" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>2391</v>
+      </c>
+      <c r="B324" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>2120</v>
+      </c>
+      <c r="B325" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>2214</v>
+      </c>
+      <c r="B326" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>2617</v>
+      </c>
+      <c r="B327" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>2610</v>
+      </c>
+      <c r="B328" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>2275</v>
+      </c>
+      <c r="B329" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>2490</v>
+      </c>
+      <c r="B330" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>2397</v>
+      </c>
+      <c r="B331" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>2523</v>
+      </c>
+      <c r="B332" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>2529</v>
+      </c>
+      <c r="B333" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>2370</v>
+      </c>
+      <c r="B334" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>2376</v>
+      </c>
+      <c r="B335" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>2598</v>
+      </c>
+      <c r="B336" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>2655</v>
+      </c>
+      <c r="B337" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>2278</v>
+      </c>
+      <c r="B338" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>2328</v>
+      </c>
+      <c r="B339" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>2605</v>
+      </c>
+      <c r="B340" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>2392</v>
+      </c>
+      <c r="B341" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>2121</v>
+      </c>
+      <c r="B342" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>2215</v>
+      </c>
+      <c r="B343" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>2618</v>
+      </c>
+      <c r="B344" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>2611</v>
+      </c>
+      <c r="B345" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>2276</v>
+      </c>
+      <c r="B346" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>2491</v>
+      </c>
+      <c r="B347" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>2398</v>
+      </c>
+      <c r="B348" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>2524</v>
+      </c>
+      <c r="B349" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>2530</v>
+      </c>
+      <c r="B350" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>2373</v>
+      </c>
+      <c r="B351" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>2377</v>
+      </c>
+      <c r="B352" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>2599</v>
+      </c>
+      <c r="B353" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>2657</v>
+      </c>
+      <c r="B354" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>2279</v>
+      </c>
+      <c r="B355" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>2107</v>
+      </c>
+      <c r="B356" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>2096</v>
+      </c>
+      <c r="B357" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>2084</v>
+      </c>
+      <c r="B358" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>2109</v>
+      </c>
+      <c r="B359" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>2156</v>
+      </c>
+      <c r="B360" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>2144</v>
+      </c>
+      <c r="B361" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>2091</v>
+      </c>
+      <c r="B362" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>2162</v>
+      </c>
+      <c r="B363" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>2086</v>
+      </c>
+      <c r="B364" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>2085</v>
+      </c>
+      <c r="B365" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>2087</v>
+      </c>
+      <c r="B366" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>2088</v>
+      </c>
+      <c r="B367" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>2082</v>
+      </c>
+      <c r="B368" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>2083</v>
+      </c>
+      <c r="B369" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>2095</v>
+      </c>
+      <c r="B370" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>2661</v>
+      </c>
+      <c r="B371" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>2165</v>
+      </c>
+      <c r="B372" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>2169</v>
+      </c>
+      <c r="B373" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>2065</v>
+      </c>
+      <c r="B374" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>2057</v>
+      </c>
+      <c r="B375" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>2122</v>
+      </c>
+      <c r="B376" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>2160</v>
+      </c>
+      <c r="B377" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>2664</v>
+      </c>
+      <c r="B378" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>2066</v>
+      </c>
+      <c r="B379" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>2163</v>
+      </c>
+      <c r="B380" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>2061</v>
+      </c>
+      <c r="B381" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>2060</v>
+      </c>
+      <c r="B382" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>2062</v>
+      </c>
+      <c r="B383" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>2063</v>
+      </c>
+      <c r="B384" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>2058</v>
+      </c>
+      <c r="B385" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>2059</v>
+      </c>
+      <c r="B386" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>2064</v>
+      </c>
+      <c r="B387" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>2662</v>
+      </c>
+      <c r="B388" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>2166</v>
+      </c>
+      <c r="B389" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>2170</v>
+      </c>
+      <c r="B390" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>2075</v>
+      </c>
+      <c r="B391" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>2069</v>
+      </c>
+      <c r="B392" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>2123</v>
+      </c>
+      <c r="B393" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>2161</v>
+      </c>
+      <c r="B394" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>2668</v>
+      </c>
+      <c r="B395" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>2076</v>
+      </c>
+      <c r="B396" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>2164</v>
+      </c>
+      <c r="B397" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>2071</v>
+      </c>
+      <c r="B398" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>2070</v>
+      </c>
+      <c r="B399" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>2072</v>
+      </c>
+      <c r="B400" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>2073</v>
+      </c>
+      <c r="B401" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>2067</v>
+      </c>
+      <c r="B402" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>2068</v>
+      </c>
+      <c r="B403" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>2074</v>
+      </c>
+      <c r="B404" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>2666</v>
+      </c>
+      <c r="B405" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>2167</v>
+      </c>
+      <c r="B406" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>2329</v>
+      </c>
+      <c r="B407" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>2606</v>
+      </c>
+      <c r="B408" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>2393</v>
+      </c>
+      <c r="B409" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>2125</v>
+      </c>
+      <c r="B410" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>2332</v>
+      </c>
+      <c r="B411" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>2667</v>
+      </c>
+      <c r="B412" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>2612</v>
+      </c>
+      <c r="B413" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>2335</v>
+      </c>
+      <c r="B414" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>2492</v>
+      </c>
+      <c r="B415" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>2399</v>
+      </c>
+      <c r="B416" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>2525</v>
+      </c>
+      <c r="B417" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>2531</v>
+      </c>
+      <c r="B418" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>2371</v>
+      </c>
+      <c r="B419" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>2378</v>
+      </c>
+      <c r="B420" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>2600</v>
+      </c>
+      <c r="B421" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>2645</v>
+      </c>
+      <c r="B422" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>2280</v>
+      </c>
+      <c r="B423" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>2330</v>
+      </c>
+      <c r="B424" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>2607</v>
+      </c>
+      <c r="B425" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>2394</v>
+      </c>
+      <c r="B426" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>2126</v>
+      </c>
+      <c r="B427" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>2333</v>
+      </c>
+      <c r="B428" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>2620</v>
+      </c>
+      <c r="B429" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>2613</v>
+      </c>
+      <c r="B430" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>2336</v>
+      </c>
+      <c r="B431" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>2493</v>
+      </c>
+      <c r="B432" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>2400</v>
+      </c>
+      <c r="B433" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>2526</v>
+      </c>
+      <c r="B434" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>2532</v>
+      </c>
+      <c r="B435" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>2372</v>
+      </c>
+      <c r="B436" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>2379</v>
+      </c>
+      <c r="B437" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>2601</v>
+      </c>
+      <c r="B438" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>2670</v>
+      </c>
+      <c r="B439" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>2281</v>
+      </c>
+      <c r="B440" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>2331</v>
+      </c>
+      <c r="B441" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>2608</v>
+      </c>
+      <c r="B442" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>2395</v>
+      </c>
+      <c r="B443" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>2127</v>
+      </c>
+      <c r="B444" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>2334</v>
+      </c>
+      <c r="B445" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>2621</v>
+      </c>
+      <c r="B446" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>2614</v>
+      </c>
+      <c r="B447" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>2337</v>
+      </c>
+      <c r="B448" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>2494</v>
+      </c>
+      <c r="B449" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>2401</v>
+      </c>
+      <c r="B450" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>2527</v>
+      </c>
+      <c r="B451" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>2533</v>
+      </c>
+      <c r="B452" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>2374</v>
+      </c>
+      <c r="B453" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>2380</v>
+      </c>
+      <c r="B454" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>2602</v>
+      </c>
+      <c r="B455" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>2671</v>
+      </c>
+      <c r="B456" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>2282</v>
+      </c>
+      <c r="B457" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>2411</v>
+      </c>
+      <c r="B458" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>2674</v>
+      </c>
+      <c r="B459" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>2504</v>
+      </c>
+      <c r="B460" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>2543</v>
+      </c>
+      <c r="B461" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>2128</v>
+      </c>
+      <c r="B462" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>2588</v>
+      </c>
+      <c r="B463" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>2673</v>
+      </c>
+      <c r="B464" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>2561</v>
+      </c>
+      <c r="B465" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>2420</v>
+      </c>
+      <c r="B466" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>2534</v>
+      </c>
+      <c r="B467" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>2552</v>
+      </c>
+      <c r="B468" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>2513</v>
+      </c>
+      <c r="B469" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>2462</v>
+      </c>
+      <c r="B470" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>2471</v>
+      </c>
+      <c r="B471" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>2570</v>
+      </c>
+      <c r="B472" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>2381</v>
+      </c>
+      <c r="B473" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>2701</v>
+      </c>
+      <c r="B474" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>2444</v>
+      </c>
+      <c r="B475" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>2412</v>
+      </c>
+      <c r="B476" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>2677</v>
+      </c>
+      <c r="B477" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>2505</v>
+      </c>
+      <c r="B478" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>2544</v>
+      </c>
+      <c r="B479" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>2129</v>
+      </c>
+      <c r="B480" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>2589</v>
+      </c>
+      <c r="B481" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>2675</v>
+      </c>
+      <c r="B482" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>2562</v>
+      </c>
+      <c r="B483" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>2421</v>
+      </c>
+      <c r="B484" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>2535</v>
+      </c>
+      <c r="B485" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>2553</v>
+      </c>
+      <c r="B486" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>2514</v>
+      </c>
+      <c r="B487" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>2463</v>
+      </c>
+      <c r="B488" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>2472</v>
+      </c>
+      <c r="B489" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>2571</v>
+      </c>
+      <c r="B490" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>2382</v>
+      </c>
+      <c r="B491" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>2702</v>
+      </c>
+      <c r="B492" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>2445</v>
+      </c>
+      <c r="B493" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>2413</v>
+      </c>
+      <c r="B494" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>2678</v>
+      </c>
+      <c r="B495" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>2506</v>
+      </c>
+      <c r="B496" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>2545</v>
+      </c>
+      <c r="B497" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>2130</v>
+      </c>
+      <c r="B498" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>2590</v>
+      </c>
+      <c r="B499" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>2676</v>
+      </c>
+      <c r="B500" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <v>2563</v>
+      </c>
+      <c r="B501" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>2422</v>
+      </c>
+      <c r="B502" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <v>2536</v>
+      </c>
+      <c r="B503" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>2554</v>
+      </c>
+      <c r="B504" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <v>2515</v>
+      </c>
+      <c r="B505" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>2464</v>
+      </c>
+      <c r="B506" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <v>2473</v>
+      </c>
+      <c r="B507" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>2572</v>
+      </c>
+      <c r="B508" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A509">
+        <v>2383</v>
+      </c>
+      <c r="B509" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A510">
+        <v>2703</v>
+      </c>
+      <c r="B510" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A511">
+        <v>2446</v>
+      </c>
+      <c r="B511" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A512">
+        <v>2414</v>
+      </c>
+      <c r="B512" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A513">
+        <v>2582</v>
+      </c>
+      <c r="B513" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A514">
+        <v>2507</v>
+      </c>
+      <c r="B514" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A515">
+        <v>2546</v>
+      </c>
+      <c r="B515" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A516">
+        <v>2131</v>
+      </c>
+      <c r="B516" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A517">
+        <v>2591</v>
+      </c>
+      <c r="B517" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A518">
+        <v>2694</v>
+      </c>
+      <c r="B518" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A519">
+        <v>2564</v>
+      </c>
+      <c r="B519" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A520">
+        <v>2423</v>
+      </c>
+      <c r="B520" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>2537</v>
+      </c>
+      <c r="B521" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A522">
+        <v>2555</v>
+      </c>
+      <c r="B522" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A523">
+        <v>2516</v>
+      </c>
+      <c r="B523" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A524">
+        <v>2465</v>
+      </c>
+      <c r="B524" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>2474</v>
+      </c>
+      <c r="B525" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A526">
+        <v>2573</v>
+      </c>
+      <c r="B526" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A527">
+        <v>2384</v>
+      </c>
+      <c r="B527" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A528">
+        <v>2705</v>
+      </c>
+      <c r="B528" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A529">
+        <v>2447</v>
+      </c>
+      <c r="B529" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A530">
+        <v>2415</v>
+      </c>
+      <c r="B530" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A531">
+        <v>2583</v>
+      </c>
+      <c r="B531" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A532">
+        <v>2508</v>
+      </c>
+      <c r="B532" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A533">
+        <v>2547</v>
+      </c>
+      <c r="B533" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A534">
+        <v>2132</v>
+      </c>
+      <c r="B534" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A535">
+        <v>2592</v>
+      </c>
+      <c r="B535" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A536">
+        <v>2695</v>
+      </c>
+      <c r="B536" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A537">
+        <v>2565</v>
+      </c>
+      <c r="B537" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A538">
+        <v>2424</v>
+      </c>
+      <c r="B538" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A539">
+        <v>2538</v>
+      </c>
+      <c r="B539" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A540">
+        <v>2556</v>
+      </c>
+      <c r="B540" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A541">
+        <v>2517</v>
+      </c>
+      <c r="B541" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A542">
+        <v>2466</v>
+      </c>
+      <c r="B542" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A543">
+        <v>2475</v>
+      </c>
+      <c r="B543" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A544">
+        <v>2574</v>
+      </c>
+      <c r="B544" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A545">
+        <v>2385</v>
+      </c>
+      <c r="B545" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A546">
+        <v>2707</v>
+      </c>
+      <c r="B546" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A547">
+        <v>2448</v>
+      </c>
+      <c r="B547" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A548">
+        <v>2416</v>
+      </c>
+      <c r="B548" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A549">
+        <v>2584</v>
+      </c>
+      <c r="B549" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A550">
+        <v>2509</v>
+      </c>
+      <c r="B550" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A551">
+        <v>2548</v>
+      </c>
+      <c r="B551" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A552">
+        <v>2133</v>
+      </c>
+      <c r="B552" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A553">
+        <v>2593</v>
+      </c>
+      <c r="B553" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A554">
+        <v>2696</v>
+      </c>
+      <c r="B554" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A555">
+        <v>2566</v>
+      </c>
+      <c r="B555" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A556">
+        <v>2425</v>
+      </c>
+      <c r="B556" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A557">
+        <v>2539</v>
+      </c>
+      <c r="B557" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A558">
+        <v>2557</v>
+      </c>
+      <c r="B558" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A559">
+        <v>2518</v>
+      </c>
+      <c r="B559" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A560">
+        <v>2467</v>
+      </c>
+      <c r="B560" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A561">
+        <v>2476</v>
+      </c>
+      <c r="B561" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A562">
+        <v>2575</v>
+      </c>
+      <c r="B562" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A563">
+        <v>2386</v>
+      </c>
+      <c r="B563" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A564">
+        <v>2706</v>
+      </c>
+      <c r="B564" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A565">
+        <v>2449</v>
+      </c>
+      <c r="B565" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A566">
+        <v>2672</v>
+      </c>
+      <c r="B566" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A567">
+        <v>1325</v>
+      </c>
+      <c r="B567" t="s">
+        <v>564</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
